--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO EGIDO PINTOBASKET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO EGIDO PINTOBASKET.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>35.3659</v>
+        <v>27.5881</v>
       </c>
       <c r="E2" t="n">
-        <v>38.5174</v>
+        <v>28.5705</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.1519</v>
+        <v>-0.9827000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-7.2846</v>
@@ -610,13 +610,13 @@
         <v>28.7167</v>
       </c>
       <c r="S2" t="n">
-        <v>13.6548</v>
+        <v>5.8771</v>
       </c>
       <c r="T2" t="n">
-        <v>14.5002</v>
+        <v>4.5533</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8452</v>
+        <v>1.3237</v>
       </c>
       <c r="V2" t="n">
         <v>33.8462</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>26.0243</v>
+        <v>23.2774</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2098</v>
+        <v>11.1341</v>
       </c>
       <c r="F3" t="n">
-        <v>12.8143</v>
+        <v>12.1434</v>
       </c>
       <c r="G3" t="n">
         <v>-10.7878</v>
@@ -688,13 +688,13 @@
         <v>52.5826</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5069</v>
+        <v>2.7603</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4319999999999999</v>
+        <v>-1.644</v>
       </c>
       <c r="U3" t="n">
-        <v>5.0751</v>
+        <v>4.404</v>
       </c>
       <c r="V3" t="n">
         <v>18.6929</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>6.637799999999999</v>
+        <v>8.020899999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3697</v>
+        <v>-7.375400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7321000000000004</v>
+        <v>15.396</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.362800000000001</v>
+        <v>-0.5747000000000018</v>
       </c>
       <c r="H4" t="n">
-        <v>-18.809</v>
+        <v>-0.3478999999999993</v>
       </c>
       <c r="I4" t="n">
-        <v>11.4462</v>
+        <v>-0.2265999999999996</v>
       </c>
       <c r="J4" t="n">
-        <v>18.5425</v>
+        <v>20.5321</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3950000000000005</v>
+        <v>13.7508</v>
       </c>
       <c r="L4" t="n">
-        <v>18.9375</v>
+        <v>6.781</v>
       </c>
       <c r="M4" t="n">
-        <v>-25.9056</v>
+        <v>-21.1064</v>
       </c>
       <c r="N4" t="n">
-        <v>-18.4141</v>
+        <v>-14.0987</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.491</v>
+        <v>-7.007400000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4926</v>
+        <v>7.9554</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.3734</v>
+        <v>-36.6724</v>
       </c>
       <c r="R4" t="n">
-        <v>36.8662</v>
+        <v>44.6279</v>
       </c>
       <c r="S4" t="n">
-        <v>12.9217</v>
+        <v>3.2395</v>
       </c>
       <c r="T4" t="n">
-        <v>8.3653</v>
+        <v>-1.4902</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5566</v>
+        <v>4.7299</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4136</v>
+        <v>-2.5996</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8358</v>
+        <v>10.2552</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.2493</v>
+        <v>-12.8548</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>G. PACHECO TABERNERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5.083499999999999</v>
+        <v>1.1479</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.879400000000002</v>
+        <v>0.2887</v>
       </c>
       <c r="F5" t="n">
-        <v>13.9628</v>
+        <v>0.8592</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5747000000000018</v>
+        <v>0.6655</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3478999999999993</v>
+        <v>0.07990000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2265999999999996</v>
+        <v>0.5856</v>
       </c>
       <c r="J5" t="n">
-        <v>20.5321</v>
+        <v>0.6941999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>13.7508</v>
+        <v>0.103</v>
       </c>
       <c r="L5" t="n">
-        <v>6.781</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-21.1064</v>
+        <v>-0.0287</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.0987</v>
+        <v>-0.02300000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.007400000000001</v>
+        <v>-0.005500000000000005</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9554</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.6724</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>44.6279</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3023999999999997</v>
+        <v>-0.115</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.9943</v>
+        <v>-0.4055</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2968</v>
+        <v>0.2905</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5996</v>
+        <v>-0.1788</v>
       </c>
       <c r="W5" t="n">
-        <v>10.2552</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.8548</v>
+        <v>-0.1788</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>D. SÁNCHEZ FRESNILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4709</v>
+        <v>-0.04649999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8925999999999995</v>
+        <v>-0.9060999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3.363699999999999</v>
+        <v>0.8596</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.127000000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.273700000000001</v>
+        <v>-0.4177</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.8537</v>
+        <v>0.7484999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>20.8525</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>16.1235</v>
+        <v>-0.3337000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>4.7291</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-26.9797</v>
+        <v>0.5833</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.3973</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.5824</v>
+        <v>0.6673</v>
       </c>
       <c r="P6" t="n">
-        <v>11.254</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.4037</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>43.6574</v>
+        <v>1.3583</v>
       </c>
       <c r="S6" t="n">
-        <v>14.469</v>
+        <v>0.3552</v>
       </c>
       <c r="T6" t="n">
-        <v>9.8164</v>
+        <v>0.0344</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6527</v>
+        <v>0.3208</v>
       </c>
       <c r="V6" t="n">
-        <v>-17.1247</v>
+        <v>-1.1206</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8417000000000001</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>-17.9667</v>
+        <v>-1.4027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PACHECO TABERNERO</t>
+          <t>I. COMENDADOR ROJAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0567</v>
+        <v>-1.2674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0885</v>
+        <v>-0.8284</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9681999999999999</v>
+        <v>-0.439</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6655</v>
+        <v>-1.3252</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07990000000000001</v>
+        <v>-0.5133</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5856</v>
+        <v>-0.8119</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6941999999999999</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.103</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5911999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0287</v>
+        <v>-0.6785</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02300000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.005500000000000005</v>
+        <v>-0.8119</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2061</v>
+        <v>-0.1363</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>-0.1817</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3995</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1788</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SÁNCHEZ FRESNILLO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0007999999999999119</v>
+        <v>-3.697399999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8060000000000003</v>
+        <v>0.4468999999999996</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8051999999999999</v>
+        <v>-4.1444</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3309</v>
+        <v>-7.362800000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4177</v>
+        <v>-18.809</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7484999999999999</v>
+        <v>11.4462</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2524999999999999</v>
+        <v>18.5425</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3337000000000001</v>
+        <v>-0.3950000000000005</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08119999999999999</v>
+        <v>18.9375</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5833</v>
+        <v>-25.9056</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-18.4141</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6673</v>
+        <v>-7.491</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>3.4926</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-33.3734</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3583</v>
+        <v>36.8662</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4008</v>
+        <v>2.5862</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1345</v>
+        <v>1.4425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2663</v>
+        <v>1.1442</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1206</v>
+        <v>-2.4136</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>13.8358</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4027</v>
+        <v>-16.2493</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. COMENDADOR ROJAS</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2947</v>
+        <v>-3.976000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8284</v>
+        <v>-11.6113</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4663</v>
+        <v>7.6357</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3252</v>
+        <v>-1.6709</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5133</v>
+        <v>-6.866000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8119</v>
+        <v>5.1954</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>3.8921</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>1.0713</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.821</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6785</v>
+        <v>-5.5632</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1335</v>
+        <v>-7.9373</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8119</v>
+        <v>2.3746</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-0.5819000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-20.3736</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>19.7917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1635</v>
+        <v>1.5407</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>0.06980000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0182</v>
+        <v>1.4705</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-3.263500000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4.8001</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-8.063600000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.2846</v>
+        <v>-4.522599999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7609000000000001</v>
+        <v>-7.836500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.523400000000001</v>
+        <v>3.314100000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.133100000000001</v>
+        <v>-6.127000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.300399999999999</v>
+        <v>-1.273700000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8325</v>
+        <v>-4.8537</v>
       </c>
       <c r="J10" t="n">
-        <v>6.8523</v>
+        <v>20.8525</v>
       </c>
       <c r="K10" t="n">
-        <v>6.0884</v>
+        <v>16.1235</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7635999999999999</v>
+        <v>4.7291</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.9852</v>
+        <v>-26.9797</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.388999999999999</v>
+        <v>-17.3973</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5961</v>
+        <v>-9.5824</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2984</v>
+        <v>11.254</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.925599999999999</v>
+        <v>-32.4037</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2242</v>
+        <v>43.6574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2750000000000001</v>
+        <v>7.4754</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1259</v>
+        <v>2.8725</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8509000000000001</v>
+        <v>4.6031</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.725000000000001</v>
+        <v>-17.1247</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1865</v>
+        <v>0.8417000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.9115</v>
+        <v>-17.9667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.7917</v>
+        <v>-7.126800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-16.5794</v>
+        <v>6.770600000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7879</v>
+        <v>-13.8975</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6709</v>
+        <v>7.888599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.866000000000001</v>
+        <v>1.9039</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1954</v>
+        <v>5.985099999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8921</v>
+        <v>37.5184</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0713</v>
+        <v>18.492</v>
       </c>
       <c r="L11" t="n">
-        <v>2.821</v>
+        <v>19.0265</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.5632</v>
+        <v>-29.6297</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.9373</v>
+        <v>-16.5882</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3746</v>
+        <v>-13.0413</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5819000000000001</v>
+        <v>-2.7165</v>
       </c>
       <c r="Q11" t="n">
-        <v>-20.3736</v>
+        <v>-41.9109</v>
       </c>
       <c r="R11" t="n">
-        <v>19.7917</v>
+        <v>39.1945</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.2752</v>
+        <v>-1.9644</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.8982</v>
+        <v>-5.206799999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3770999999999998</v>
+        <v>3.2424</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.263500000000001</v>
+        <v>-10.3347</v>
       </c>
       <c r="W11" t="n">
-        <v>4.8001</v>
+        <v>16.3699</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.063600000000001</v>
+        <v>-26.7045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. RUEDA ALVAREZ</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.0337</v>
+        <v>-8.154499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0454</v>
+        <v>-13.3153</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.9883</v>
+        <v>5.160699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>5.5734</v>
+        <v>-4.704</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8201</v>
+        <v>-3.9729</v>
       </c>
       <c r="I12" t="n">
-        <v>8.3934</v>
+        <v>-0.7315</v>
       </c>
       <c r="J12" t="n">
-        <v>8.7928</v>
+        <v>13.2661</v>
       </c>
       <c r="K12" t="n">
-        <v>2.434699999999999</v>
+        <v>8.963900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>6.3582</v>
+        <v>4.302200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2194</v>
+        <v>-17.9704</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.254799999999999</v>
+        <v>-12.9366</v>
       </c>
       <c r="O12" t="n">
-        <v>2.0354</v>
+        <v>-5.033300000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.238899999999999</v>
+        <v>0.3880999999999994</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.3584</v>
+        <v>-34.7319</v>
       </c>
       <c r="R12" t="n">
-        <v>9.1195</v>
+        <v>35.1197</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0579</v>
+        <v>3.7389</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.641</v>
+        <v>-0.8374999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4168</v>
+        <v>4.5765</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.3104</v>
+        <v>-7.5776</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1611</v>
+        <v>8.988</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.4717</v>
+        <v>-16.5656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>D. RUEDA ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.1436</v>
+        <v>-9.245199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.5827</v>
+        <v>-4.1235</v>
       </c>
       <c r="F13" t="n">
-        <v>4.438999999999999</v>
+        <v>-5.1219</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.704</v>
+        <v>5.5734</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9729</v>
+        <v>-2.8201</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7315</v>
+        <v>8.3934</v>
       </c>
       <c r="J13" t="n">
-        <v>13.2661</v>
+        <v>8.7928</v>
       </c>
       <c r="K13" t="n">
-        <v>8.963900000000001</v>
+        <v>2.434699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.302200000000001</v>
+        <v>6.3582</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.9704</v>
+        <v>-3.2194</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.9366</v>
+        <v>-5.254799999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.033300000000001</v>
+        <v>2.0354</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3880999999999994</v>
+        <v>-5.238899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-34.7319</v>
+        <v>-14.3584</v>
       </c>
       <c r="R13" t="n">
-        <v>35.1197</v>
+        <v>9.1195</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2499</v>
+        <v>-3.2694</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.1048</v>
+        <v>-0.7189999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8547</v>
+        <v>-2.5503</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.5776</v>
+        <v>-6.3104</v>
       </c>
       <c r="W13" t="n">
-        <v>8.988</v>
+        <v>2.1611</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.5656</v>
+        <v>-8.4717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.449</v>
+        <v>-11.7198</v>
       </c>
       <c r="E14" t="n">
-        <v>1.481699999999998</v>
+        <v>-2.7629</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.9303</v>
+        <v>-8.956899999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>7.888599999999999</v>
+        <v>-4.133100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9039</v>
+        <v>-3.300399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>5.985099999999999</v>
+        <v>-0.8325</v>
       </c>
       <c r="J14" t="n">
-        <v>37.5184</v>
+        <v>6.8523</v>
       </c>
       <c r="K14" t="n">
-        <v>18.492</v>
+        <v>6.0884</v>
       </c>
       <c r="L14" t="n">
-        <v>19.0265</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-29.6297</v>
+        <v>-10.9852</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.5882</v>
+        <v>-9.388999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.0413</v>
+        <v>-1.5961</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7165</v>
+        <v>3.2984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-41.9109</v>
+        <v>-8.925599999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>39.1945</v>
+        <v>12.2242</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.2864</v>
+        <v>-1.1603</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.4963</v>
+        <v>-0.8760999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2096</v>
+        <v>-0.2841</v>
       </c>
       <c r="V14" t="n">
-        <v>-10.3347</v>
+        <v>-9.725000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>16.3699</v>
+        <v>0.1865</v>
       </c>
       <c r="X14" t="n">
-        <v>-26.7045</v>
+        <v>-9.9115</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>-18.6953</v>
+        <v>-16.8882</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.2603</v>
+        <v>-13.6762</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.435</v>
+        <v>-3.2121</v>
       </c>
       <c r="G15" t="n">
         <v>-3.1467</v>
@@ -1624,13 +1624,13 @@
         <v>28.717</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5274</v>
+        <v>4.3344</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4020000000000001</v>
+        <v>2.1821</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9294</v>
+        <v>2.152</v>
       </c>
       <c r="V15" t="n">
         <v>-9.1502</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-26.3984</v>
+        <v>-18.0991</v>
       </c>
       <c r="E16" t="n">
-        <v>-25.5821</v>
+        <v>-20.6326</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8164000000000005</v>
+        <v>2.533600000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-11.0533</v>
@@ -1702,13 +1702,13 @@
         <v>45.5975</v>
       </c>
       <c r="S16" t="n">
-        <v>-13.7119</v>
+        <v>-5.4128</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.9407</v>
+        <v>-3.9912</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.771</v>
+        <v>-1.4214</v>
       </c>
       <c r="V16" t="n">
         <v>0.3071999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-42.0731</v>
+        <v>-34.8642</v>
       </c>
       <c r="E17" t="n">
-        <v>-32.4983</v>
+        <v>-24.2454</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.5748</v>
+        <v>-10.619</v>
       </c>
       <c r="G17" t="n">
         <v>-9.575099999999999</v>
@@ -1780,13 +1780,13 @@
         <v>43.8515</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.5614</v>
+        <v>-3.3526</v>
       </c>
       <c r="T17" t="n">
-        <v>-13.9664</v>
+        <v>-5.7137</v>
       </c>
       <c r="U17" t="n">
-        <v>3.4052</v>
+        <v>2.3609</v>
       </c>
       <c r="V17" t="n">
         <v>-20.3845</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-70.5258</v>
+        <v>-59.57340000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-65.04839999999999</v>
+        <v>-60.10280000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.477400000000003</v>
+        <v>0.5287999999999968</v>
       </c>
       <c r="G18" t="n">
         <v>-53.2868</v>
@@ -1828,7 +1828,7 @@
         <v>-51.8139</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.472700000000003</v>
+        <v>-1.472700000000004</v>
       </c>
       <c r="J18" t="n">
         <v>201.1593</v>
@@ -1837,7 +1837,7 @@
         <v>131.1641</v>
       </c>
       <c r="L18" t="n">
-        <v>69.99499999999999</v>
+        <v>69.995</v>
       </c>
       <c r="M18" t="n">
         <v>-254.4461</v>
@@ -1858,13 +1858,13 @@
         <v>442.3948</v>
       </c>
       <c r="S18" t="n">
-        <v>5.545699999999997</v>
+        <v>16.4969</v>
       </c>
       <c r="T18" t="n">
-        <v>-14.8568</v>
+        <v>-9.911099999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>20.4031</v>
+        <v>26.4081</v>
       </c>
       <c r="V18" t="n">
         <v>-37.3369</v>
